--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486803_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486803_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.132300000000001</v>
+        <v>7.8153</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4437</v>
+        <v>5.8784</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6886</v>
+        <v>1.9369</v>
       </c>
       <c r="G2" t="n">
         <v>2.3343</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0683</v>
+        <v>1.7513</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1233</v>
+        <v>1.5579</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0549</v>
+        <v>0.1934</v>
       </c>
       <c r="V2" t="n">
         <v>1.7989</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.257</v>
+        <v>7.5563</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3437</v>
+        <v>5.7986</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9133</v>
+        <v>1.7577</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0455</v>
+        <v>2.9052</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4072</v>
+        <v>1.5036</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3618</v>
+        <v>1.4016</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3156</v>
+        <v>3.6302</v>
       </c>
       <c r="K3" t="n">
-        <v>2.339</v>
+        <v>1.0213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9766</v>
+        <v>2.6089</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2701</v>
+        <v>-0.725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0682</v>
+        <v>0.4822</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3384</v>
+        <v>-1.2072</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6516</v>
+        <v>0.3654</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3989</v>
+        <v>-0.5726</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2526</v>
+        <v>0.9381</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3709</v>
+        <v>2.741</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3709</v>
+        <v>2.741</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.1908</v>
+        <v>5.4809</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4331</v>
+        <v>3.5925</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7577</v>
+        <v>1.8885</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9052</v>
+        <v>2.0455</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5036</v>
+        <v>2.4072</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4016</v>
+        <v>-0.3618</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6302</v>
+        <v>3.3156</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0213</v>
+        <v>2.339</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6089</v>
+        <v>0.9766</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.725</v>
+        <v>-1.2701</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4822</v>
+        <v>0.0682</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2072</v>
+        <v>-1.3384</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.8755</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9381</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9381</v>
+        <v>1.2278</v>
       </c>
       <c r="V4" t="n">
-        <v>2.741</v>
+        <v>-0.3709</v>
       </c>
       <c r="W4" t="n">
-        <v>2.741</v>
+        <v>-0.3709</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6068</v>
+        <v>4.9948</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3443</v>
+        <v>3.3752</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2625</v>
+        <v>1.6196</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3545</v>
+        <v>2.2405</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>2.1727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8455</v>
+        <v>0.0679</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3348</v>
+        <v>2.421</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0627</v>
+        <v>1.9665</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7279</v>
+        <v>0.4545</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0197</v>
+        <v>-0.1805</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1373</v>
+        <v>0.2061</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1176</v>
+        <v>-0.3866</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6731</v>
+        <v>1.6963</v>
       </c>
       <c r="T5" t="n">
-        <v>0.11</v>
+        <v>1.0201</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5631</v>
+        <v>0.6762</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W5" t="n">
         <v>0.8995</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3282</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.596</v>
+        <v>4.3956</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1333</v>
+        <v>2.282</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4627</v>
+        <v>2.1136</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1325</v>
+        <v>0.3545</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4898</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6427</v>
+        <v>-0.8455</v>
       </c>
       <c r="J6" t="n">
-        <v>4.9264</v>
+        <v>0.3348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9386</v>
+        <v>1.0627</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9878</v>
+        <v>-0.7279</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7939000000000001</v>
+        <v>0.0197</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5513</v>
+        <v>0.1373</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3451</v>
+        <v>-0.1176</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3515</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07729999999999999</v>
+        <v>1.4619</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8277</v>
+        <v>1.0477</v>
       </c>
       <c r="U6" t="n">
-        <v>0.905</v>
+        <v>0.4141</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6138</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4973</v>
+        <v>3.8083</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5549</v>
+        <v>3.3953</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9424</v>
+        <v>0.413</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2405</v>
+        <v>4.1325</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1727</v>
+        <v>1.4898</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0679</v>
+        <v>2.6427</v>
       </c>
       <c r="J7" t="n">
-        <v>2.421</v>
+        <v>4.9264</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9665</v>
+        <v>0.9386</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4545</v>
+        <v>3.9878</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1805</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2061</v>
+        <v>0.5513</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3866</v>
+        <v>-1.3451</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1988</v>
+        <v>0.2896</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8002</v>
+        <v>-0.5657</v>
       </c>
       <c r="U7" t="n">
-        <v>0.999</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2856</v>
+        <v>-0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-0.6138</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0265</v>
+        <v>2.5563</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7737</v>
+        <v>1.1049</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2527</v>
+        <v>1.4514</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0774</v>
@@ -1078,13 +1078,13 @@
         <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3662</v>
+        <v>1.8961</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2336</v>
+        <v>1.5649</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1326</v>
+        <v>0.3312</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6181</v>
+        <v>1.0469</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3933</v>
+        <v>0.2342</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0114</v>
+        <v>0.8127</v>
       </c>
       <c r="G9" t="n">
         <v>-0.877</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1436</v>
+        <v>0.5724</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0485</v>
+        <v>-0.421</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1921</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2551</v>
+        <v>0.5089</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2282</v>
+        <v>-1.1731</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4833</v>
+        <v>1.682</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7047</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1987</v>
+        <v>0.0552</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7725</v>
+        <v>-0.7174</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5739</v>
+        <v>0.7725</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0453</v>
+        <v>-0.2011</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1593</v>
+        <v>-1.4144</v>
       </c>
       <c r="F11" t="n">
-        <v>1.114</v>
+        <v>1.2133</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0065</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8108</v>
+        <v>0.655</v>
       </c>
       <c r="T11" t="n">
-        <v>0.965</v>
+        <v>0.71</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1543</v>
+        <v>-0.0549</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6565</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>37.13460000000001</v>
+        <v>37.9622</v>
       </c>
       <c r="E12" t="n">
-        <v>22.2459</v>
+        <v>23.0736</v>
       </c>
       <c r="F12" t="n">
-        <v>14.8886</v>
+        <v>14.8887</v>
       </c>
       <c r="G12" t="n">
         <v>11.3469</v>
@@ -1375,7 +1375,7 @@
         <v>-3.5265</v>
       </c>
       <c r="N12" t="n">
-        <v>3.097500000000001</v>
+        <v>3.0975</v>
       </c>
       <c r="O12" t="n">
         <v>-6.624200000000001</v>
@@ -1390,13 +1390,13 @@
         <v>14.4808</v>
       </c>
       <c r="S12" t="n">
-        <v>9.791</v>
+        <v>10.6187</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4438</v>
+        <v>4.271599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>6.3472</v>
+        <v>6.3471</v>
       </c>
       <c r="V12" t="n">
         <v>4.412</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1701</v>
+        <v>0.6049</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5896</v>
+        <v>1.0032</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7597</v>
+        <v>-0.3983</v>
       </c>
       <c r="G13" t="n">
         <v>3.4847</v>
@@ -1468,13 +1468,13 @@
         <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1955</v>
+        <v>-1.4204</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9381</v>
+        <v>-0.5244</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2574</v>
+        <v>-0.896</v>
       </c>
       <c r="V13" t="n">
         <v>0.0852</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7449</v>
+        <v>-0.6455</v>
       </c>
       <c r="E14" t="n">
         <v>2.8935</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.6383</v>
+        <v>-3.539</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8874</v>
@@ -1546,13 +1546,13 @@
         <v>0.1931</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5059</v>
+        <v>-1.4066</v>
       </c>
       <c r="T14" t="n">
         <v>-1.2692</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2367</v>
+        <v>-0.1374</v>
       </c>
       <c r="V14" t="n">
         <v>1.8415</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.5471</v>
+        <v>-1.3885</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7742</v>
+        <v>-0.8776</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.773</v>
+        <v>-0.5109</v>
       </c>
       <c r="G15" t="n">
         <v>0.8043</v>
@@ -1624,13 +1624,13 @@
         <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1584</v>
+        <v>-0.9998</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0825</v>
+        <v>-0.0209</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2409</v>
+        <v>-0.9788</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6138</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.3012</v>
+        <v>-2.8709</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1117</v>
+        <v>-1.9048</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1896</v>
+        <v>-0.9661</v>
       </c>
       <c r="G16" t="n">
         <v>0.3399</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1198</v>
+        <v>-0.6895</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.3445</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5559</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.3912</v>
+        <v>-4.2823</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.2729</v>
+        <v>-3.3764</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1183</v>
+        <v>-0.9059</v>
       </c>
       <c r="G17" t="n">
         <v>-4.3802</v>
@@ -1780,13 +1780,13 @@
         <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8605</v>
+        <v>-0.7516</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4142</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4464</v>
+        <v>-0.234</v>
       </c>
       <c r="V17" t="n">
         <v>0.6565</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.4699</v>
+        <v>-5.3209</v>
       </c>
       <c r="E18" t="n">
         <v>-2.9589</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.511</v>
+        <v>-2.362</v>
       </c>
       <c r="G18" t="n">
         <v>-3.5183</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.3586</v>
       </c>
       <c r="T18" t="n">
         <v>-0.607</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0994</v>
+        <v>0.2484</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.6391</v>
+        <v>-5.7039</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0589</v>
+        <v>-3.1624</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5801</v>
+        <v>-2.5416</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7908</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3349</v>
+        <v>-1.3998</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4142</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9208</v>
+        <v>-0.8822</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8995</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.9167</v>
+        <v>-7.6106</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4987</v>
+        <v>-1.809</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.418</v>
+        <v>-5.8016</v>
       </c>
       <c r="G20" t="n">
         <v>0.0924</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.623</v>
+        <v>-1.3168</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8556</v>
+        <v>-1.1659</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2327</v>
+        <v>-0.1509</v>
       </c>
       <c r="V20" t="n">
         <v>-3.6831</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.9542</v>
+        <v>-9.227399999999999</v>
       </c>
       <c r="E21" t="n">
         <v>-4.6964</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.2578</v>
+        <v>-4.531</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4915</v>
@@ -2092,13 +2092,13 @@
         <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4853</v>
+        <v>-0.7585</v>
       </c>
       <c r="T21" t="n">
         <v>-1.3796</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8942</v>
+        <v>0.6211</v>
       </c>
       <c r="V21" t="n">
         <v>0.0426</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-37.1344</v>
+        <v>-36.4451</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.8886</v>
+        <v>-14.8888</v>
       </c>
       <c r="F22" t="n">
-        <v>-22.2458</v>
+        <v>-21.5564</v>
       </c>
       <c r="G22" t="n">
         <v>-11.3469</v>
@@ -2170,13 +2170,13 @@
         <v>2.8963</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.790900000000001</v>
+        <v>-9.101599999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-6.3472</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.4439</v>
+        <v>-2.7543</v>
       </c>
       <c r="V22" t="n">
         <v>-4.412100000000001</v>
